--- a/docs/StructureDefinition-PASportObservationBloodPressure.xlsx
+++ b/docs/StructureDefinition-PASportObservationBloodPressure.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-28T05:34:23+08:00</t>
+    <t>2026-02-28T07:16:04+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-PASportObservationBloodPressure.xlsx
+++ b/docs/StructureDefinition-PASportObservationBloodPressure.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-28T07:16:04+08:00</t>
+    <t>2026-02-28T23:13:53+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-PASportObservationBloodPressure.xlsx
+++ b/docs/StructureDefinition-PASportObservationBloodPressure.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.4.1</t>
+    <t>1.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-28T23:13:53+08:00</t>
+    <t>2026-03-01T19:25:35+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-PASportObservationBloodPressure.xlsx
+++ b/docs/StructureDefinition-PASportObservationBloodPressure.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-01T19:25:35+08:00</t>
+    <t>2026-03-02T02:26:08+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-PASportObservationBloodPressure.xlsx
+++ b/docs/StructureDefinition-PASportObservationBloodPressure.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5101" uniqueCount="684">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5101" uniqueCount="683">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-02T02:26:08+08:00</t>
+    <t>2026-04-02T13:32:15+08:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -380,7 +380,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -625,7 +625,7 @@
     <t>Codes for high level observation categories.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-category</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-category|4.0.1</t>
   </si>
   <si>
     <t>value:coding.code}
@@ -908,10 +908,10 @@
     <t>血壓</t>
   </si>
   <si>
-    <t>A concept that may be defined by a formal reference to a terminology or ontology or may be provided by text.</t>
-  </si>
-  <si>
-    <t>Not all terminology uses fit this general pattern. In some cases, models should not use CodeableConcept and use Coding directly and provide their own structure for managing text, codings, translations and the relationship between elements and pre- and post-coordination.</t>
+    <t>Blood Pressure.</t>
+  </si>
+  <si>
+    <t>additional codes that translate or map to this code are allowed.  For example a more granular LOINC code or code that is used locally in a system.</t>
   </si>
   <si>
     <t>5. SHALL contain exactly one [1..1] code, where the @code SHOULD be selected from ValueSet HITSP Vital Sign Result Type 2.16.840.1.113883.3.88.12.80.62 DYNAMIC (CONF:7301).</t>
@@ -923,17 +923,25 @@
     <t>This identifies the vital sign result type.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-vitalsignresult</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ele-1
-</t>
-  </si>
-  <si>
-    <t>CE/CNE/CWE</t>
-  </si>
-  <si>
-    <t>CD</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-vitalsignresult|4.0.1</t>
+  </si>
+  <si>
+    <t>Event.code</t>
+  </si>
+  <si>
+    <t>&lt; 363787002 |Observable entity| OR &lt; 386053000 |Evaluation procedure|</t>
+  </si>
+  <si>
+    <t>OBX-3</t>
+  </si>
+  <si>
+    <t>code</t>
+  </si>
+  <si>
+    <t>FiveWs.what[x]</t>
+  </si>
+  <si>
+    <t>116680003 |Is a|</t>
   </si>
   <si>
     <t>Observation.code.id</t>
@@ -1040,7 +1048,7 @@
     <t>Observation.focus</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">Reference(Resource|4.0.1)
 </t>
   </si>
   <si>
@@ -1051,9 +1059,6 @@
   </si>
   <si>
     <t>Typically, an observation is made about the subject - a patient, or group of patients, location, or device - and the distinction between the subject and what is directly measured for an observation is specified in the observation code itself ( e.g., "Blood Glucose") and does not need to be represented separately using this element.  Use `specimen` if a reference to a specimen is required.  If a code is required instead of a resource use either  `bodysite` for bodysites or the standard extension [focusCode](http://hl7.org/fhir/extension-observation-focuscode.html).</t>
-  </si>
-  <si>
-    <t>OBX-3</t>
   </si>
   <si>
     <t>participation[typeCode=SBJ]</t>
@@ -1066,7 +1071,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Encounter)
+    <t xml:space="preserve">Reference(Encounter|4.0.1)
 </t>
   </si>
   <si>
@@ -1165,7 +1170,7 @@
     <t>Observation.performer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|PractitionerRole|Organization|CareTeam|Patient|RelatedPerson)
+    <t xml:space="preserve">Reference(Practitioner|4.0.1|PractitionerRole|4.0.1|Organization|4.0.1|CareTeam|4.0.1|Patient|4.0.1|RelatedPerson|4.0.1)
 </t>
   </si>
   <si>
@@ -1254,7 +1259,7 @@
     <t>Codes specifying why the result (`Observation.value[x]`) is missing.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/data-absent-reason</t>
+    <t>http://hl7.org/fhir/ValueSet/data-absent-reason|4.0.1</t>
   </si>
   <si>
     <t>obs-6
@@ -1286,7 +1291,7 @@
     <t>Codes identifying interpretations of observations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-interpretation</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-interpretation|4.0.1</t>
   </si>
   <si>
     <t>&lt; 260245000 |Findings values|</t>
@@ -1381,7 +1386,7 @@
     <t>Observation.specimen</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Specimen)
+    <t xml:space="preserve">Reference(Specimen|4.0.1)
 </t>
   </si>
   <si>
@@ -1409,7 +1414,7 @@
     <t>Observation.device</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Device|DeviceMetric)
+    <t xml:space="preserve">Reference(Device|4.0.1|DeviceMetric|4.0.1)
 </t>
   </si>
   <si>
@@ -1489,7 +1494,7 @@
     <t>Observation.referenceRange.low</t>
   </si>
   <si>
-    <t xml:space="preserve">Quantity {SimpleQuantity}
+    <t xml:space="preserve">Quantity {SimpleQuantity|4.0.1}
 </t>
   </si>
   <si>
@@ -1539,7 +1544,7 @@
     <t>Code for the meaning of a reference range.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/referencerange-meaning</t>
+    <t>http://hl7.org/fhir/ValueSet/referencerange-meaning|4.0.1</t>
   </si>
   <si>
     <t>&lt; 260245000 |Findings values| OR  @@ -1575,7 +1580,7 @@
     <t>Codes identifying the population the reference range applies to.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/referencerange-appliesto</t>
+    <t>http://hl7.org/fhir/ValueSet/referencerange-appliesto|4.0.1</t>
   </si>
   <si>
     <t>Observation.referenceRange.age</t>
@@ -1707,12 +1712,6 @@
 &lt; 386053000 |Evaluation procedure|</t>
   </si>
   <si>
-    <t>code</t>
-  </si>
-  <si>
-    <t>FiveWs.what[x]</t>
-  </si>
-  <si>
     <t>Observation.component.value[x]</t>
   </si>
   <si>
@@ -1794,9 +1793,6 @@
   </si>
   <si>
     <t>收縮壓代碼</t>
-  </si>
-  <si>
-    <t>additional codes that translate or map to this code are allowed.  For example a more granular LOINC code or code that is used locally in a system.</t>
   </si>
   <si>
     <t>Observation.component:SystolicBP.code.id</t>
@@ -2488,7 +2484,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="54.6171875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="43.5859375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="47.9921875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.4453125" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
@@ -5787,7 +5783,7 @@
         <v>20</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>20</v>
+        <v>93</v>
       </c>
       <c r="K28" t="s" s="2">
         <v>285</v>
@@ -5860,36 +5856,36 @@
         <v>92</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>293</v>
+        <v>20</v>
       </c>
       <c r="AJ28" t="s" s="2">
         <v>104</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>20</v>
+        <v>293</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>20</v>
+        <v>294</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>20</v>
+        <v>297</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>20</v>
+        <v>298</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -6004,10 +6000,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -6124,10 +6120,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -6199,7 +6195,7 @@
         <v>20</v>
       </c>
       <c r="AB31" t="s" s="2">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="AC31" s="2"/>
       <c r="AD31" t="s" s="2">
@@ -6244,13 +6240,13 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="C32" t="s" s="2">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="D32" t="s" s="2">
         <v>20</v>
@@ -6368,10 +6364,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6486,10 +6482,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6606,10 +6602,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6651,7 +6647,7 @@
       </c>
       <c r="Q35" s="2"/>
       <c r="R35" t="s" s="2">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="S35" t="s" s="2">
         <v>20</v>
@@ -6728,10 +6724,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6848,10 +6844,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6891,7 +6887,7 @@
       </c>
       <c r="Q37" s="2"/>
       <c r="R37" t="s" s="2">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="S37" t="s" s="2">
         <v>20</v>
@@ -6968,10 +6964,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -7088,10 +7084,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -7210,10 +7206,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7332,10 +7328,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7358,19 +7354,19 @@
         <v>93</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>20</v>
@@ -7419,7 +7415,7 @@
         <v>20</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -7434,19 +7430,19 @@
         <v>104</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="AP41" t="s" s="2">
         <v>20</v>
@@ -7454,10 +7450,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7480,16 +7476,16 @@
         <v>93</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -7539,7 +7535,7 @@
         <v>20</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -7560,13 +7556,13 @@
         <v>20</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>334</v>
+        <v>295</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="AP42" t="s" s="2">
         <v>20</v>
@@ -7574,14 +7570,14 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -7600,19 +7596,19 @@
         <v>93</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>20</v>
@@ -7661,7 +7657,7 @@
         <v>20</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -7676,19 +7672,19 @@
         <v>104</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="AP43" t="s" s="2">
         <v>20</v>
@@ -7696,14 +7692,14 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -7722,19 +7718,19 @@
         <v>93</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>20</v>
@@ -7783,7 +7779,7 @@
         <v>20</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7792,25 +7788,25 @@
         <v>92</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="AP44" t="s" s="2">
         <v>20</v>
@@ -7818,10 +7814,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7844,16 +7840,16 @@
         <v>93</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -7903,7 +7899,7 @@
         <v>20</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7924,13 +7920,13 @@
         <v>20</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="AP45" t="s" s="2">
         <v>20</v>
@@ -7938,10 +7934,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7964,17 +7960,17 @@
         <v>93</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>20</v>
@@ -8023,7 +8019,7 @@
         <v>20</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -8038,19 +8034,19 @@
         <v>104</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="AL46" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="AP46" t="s" s="2">
         <v>20</v>
@@ -8058,10 +8054,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8084,19 +8080,19 @@
         <v>93</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>20</v>
@@ -8133,17 +8129,17 @@
         <v>20</v>
       </c>
       <c r="AB47" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="AC47" s="2"/>
       <c r="AD47" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE47" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -8152,7 +8148,7 @@
         <v>92</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="AJ47" t="s" s="2">
         <v>104</v>
@@ -8161,30 +8157,30 @@
         <v>20</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="C48" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="D48" t="s" s="2">
         <v>20</v>
@@ -8206,19 +8202,19 @@
         <v>93</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>20</v>
@@ -8267,7 +8263,7 @@
         <v>20</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -8276,7 +8272,7 @@
         <v>92</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="AJ48" t="s" s="2">
         <v>104</v>
@@ -8285,27 +8281,27 @@
         <v>20</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8331,16 +8327,16 @@
         <v>189</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>20</v>
@@ -8368,10 +8364,10 @@
         <v>290</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>20</v>
@@ -8389,7 +8385,7 @@
         <v>20</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -8398,7 +8394,7 @@
         <v>92</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="AJ49" t="s" s="2">
         <v>104</v>
@@ -8413,7 +8409,7 @@
         <v>135</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>20</v>
@@ -8424,14 +8420,14 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
@@ -8453,16 +8449,16 @@
         <v>189</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>20</v>
@@ -8490,10 +8486,10 @@
         <v>290</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>20</v>
@@ -8511,7 +8507,7 @@
         <v>20</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -8529,27 +8525,27 @@
         <v>20</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8572,19 +8568,19 @@
         <v>20</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>20</v>
@@ -8633,7 +8629,7 @@
         <v>20</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8654,10 +8650,10 @@
         <v>20</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>20</v>
@@ -8668,10 +8664,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8697,13 +8693,13 @@
         <v>189</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -8733,7 +8729,7 @@
       </c>
       <c r="Y52" s="2"/>
       <c r="Z52" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>20</v>
@@ -8751,7 +8747,7 @@
         <v>20</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -8769,27 +8765,27 @@
         <v>20</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8815,16 +8811,16 @@
         <v>189</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>20</v>
@@ -8853,7 +8849,7 @@
       </c>
       <c r="Y53" s="2"/>
       <c r="Z53" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>20</v>
@@ -8871,7 +8867,7 @@
         <v>20</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8892,10 +8888,10 @@
         <v>20</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>20</v>
@@ -8906,10 +8902,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8932,16 +8928,16 @@
         <v>20</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8991,7 +8987,7 @@
         <v>20</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -9009,27 +9005,27 @@
         <v>20</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP54" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9052,16 +9048,16 @@
         <v>20</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -9111,7 +9107,7 @@
         <v>20</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -9129,27 +9125,27 @@
         <v>20</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP55" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9172,19 +9168,19 @@
         <v>20</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>20</v>
@@ -9233,7 +9229,7 @@
         <v>20</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -9245,7 +9241,7 @@
         <v>20</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>20</v>
@@ -9254,10 +9250,10 @@
         <v>20</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>20</v>
@@ -9268,10 +9264,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9386,10 +9382,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9506,14 +9502,14 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
@@ -9535,10 +9531,10 @@
         <v>138</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="N59" t="s" s="2">
         <v>141</v>
@@ -9593,7 +9589,7 @@
         <v>20</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -9628,10 +9624,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9654,13 +9650,13 @@
         <v>20</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -9711,7 +9707,7 @@
         <v>20</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -9720,7 +9716,7 @@
         <v>92</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="AJ60" t="s" s="2">
         <v>104</v>
@@ -9732,10 +9728,10 @@
         <v>20</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>20</v>
@@ -9746,10 +9742,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9772,13 +9768,13 @@
         <v>20</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -9829,7 +9825,7 @@
         <v>20</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -9838,7 +9834,7 @@
         <v>92</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="AJ61" t="s" s="2">
         <v>104</v>
@@ -9850,10 +9846,10 @@
         <v>20</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>20</v>
@@ -9864,10 +9860,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9893,16 +9889,16 @@
         <v>189</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>20</v>
@@ -9930,10 +9926,10 @@
         <v>116</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>20</v>
@@ -9951,7 +9947,7 @@
         <v>20</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -9969,13 +9965,13 @@
         <v>20</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>20</v>
@@ -9986,10 +9982,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10015,16 +10011,16 @@
         <v>189</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>20</v>
@@ -10049,13 +10045,13 @@
         <v>20</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>20</v>
@@ -10073,7 +10069,7 @@
         <v>20</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -10091,13 +10087,13 @@
         <v>20</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>20</v>
@@ -10108,10 +10104,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10134,17 +10130,17 @@
         <v>20</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" t="s" s="2">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>20</v>
@@ -10193,7 +10189,7 @@
         <v>20</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -10217,7 +10213,7 @@
         <v>20</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>20</v>
@@ -10228,10 +10224,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10257,10 +10253,10 @@
         <v>204</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -10311,7 +10307,7 @@
         <v>20</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -10332,10 +10328,10 @@
         <v>20</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>20</v>
@@ -10346,10 +10342,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10372,16 +10368,16 @@
         <v>93</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -10431,7 +10427,7 @@
         <v>20</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -10452,10 +10448,10 @@
         <v>20</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>20</v>
@@ -10466,10 +10462,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10492,16 +10488,16 @@
         <v>93</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -10551,7 +10547,7 @@
         <v>20</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -10572,10 +10568,10 @@
         <v>20</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>20</v>
@@ -10586,10 +10582,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10597,7 +10593,7 @@
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="G68" t="s" s="2">
         <v>81</v>
@@ -10612,19 +10608,19 @@
         <v>93</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="O68" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>20</v>
@@ -10661,7 +10657,7 @@
         <v>20</v>
       </c>
       <c r="AB68" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="AC68" s="2"/>
       <c r="AD68" t="s" s="2">
@@ -10671,7 +10667,7 @@
         <v>197</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -10683,7 +10679,7 @@
         <v>20</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>20</v>
@@ -10692,10 +10688,10 @@
         <v>20</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>20</v>
@@ -10706,10 +10702,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10824,10 +10820,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10944,14 +10940,14 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
@@ -10973,10 +10969,10 @@
         <v>138</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="N71" t="s" s="2">
         <v>141</v>
@@ -11031,7 +11027,7 @@
         <v>20</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -11066,10 +11062,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11095,16 +11091,16 @@
         <v>189</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>20</v>
@@ -11153,7 +11149,7 @@
         <v>20</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>92</v>
@@ -11171,16 +11167,16 @@
         <v>20</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>334</v>
+        <v>295</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>540</v>
+        <v>296</v>
       </c>
       <c r="AO72" t="s" s="2">
-        <v>541</v>
+        <v>297</v>
       </c>
       <c r="AP72" t="s" s="2">
         <v>20</v>
@@ -11226,7 +11222,7 @@
         <v>546</v>
       </c>
       <c r="O73" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>20</v>
@@ -11296,16 +11292,16 @@
         <v>550</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP73" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="74">
@@ -11348,7 +11344,7 @@
         <v>554</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>20</v>
@@ -11376,10 +11372,10 @@
         <v>290</v>
       </c>
       <c r="Y74" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="Z74" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>20</v>
@@ -11421,7 +11417,7 @@
         <v>135</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>20</v>
@@ -11439,7 +11435,7 @@
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
@@ -11461,16 +11457,16 @@
         <v>189</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>20</v>
@@ -11498,10 +11494,10 @@
         <v>290</v>
       </c>
       <c r="Y75" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="Z75" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>20</v>
@@ -11537,19 +11533,19 @@
         <v>20</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP75" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="76" hidden="true">
@@ -11589,10 +11585,10 @@
         <v>559</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="O76" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>20</v>
@@ -11662,10 +11658,10 @@
         <v>20</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>20</v>
@@ -11679,7 +11675,7 @@
         <v>560</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="C77" t="s" s="2">
         <v>561</v>
@@ -11704,19 +11700,19 @@
         <v>93</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="O77" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>20</v>
@@ -11765,7 +11761,7 @@
         <v>20</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
@@ -11777,7 +11773,7 @@
         <v>20</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="AK77" t="s" s="2">
         <v>20</v>
@@ -11786,10 +11782,10 @@
         <v>20</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>20</v>
@@ -11803,7 +11799,7 @@
         <v>562</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11921,7 +11917,7 @@
         <v>563</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -12041,11 +12037,11 @@
         <v>564</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
@@ -12067,10 +12063,10 @@
         <v>138</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="N80" t="s" s="2">
         <v>141</v>
@@ -12125,7 +12121,7 @@
         <v>20</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
@@ -12163,7 +12159,7 @@
         <v>565</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12192,13 +12188,13 @@
         <v>567</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>568</v>
+        <v>288</v>
       </c>
       <c r="O81" t="s" s="2">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>20</v>
@@ -12247,7 +12243,7 @@
         <v>20</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>92</v>
@@ -12265,16 +12261,16 @@
         <v>20</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>334</v>
+        <v>295</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>540</v>
+        <v>296</v>
       </c>
       <c r="AO81" t="s" s="2">
-        <v>541</v>
+        <v>297</v>
       </c>
       <c r="AP81" t="s" s="2">
         <v>20</v>
@@ -12282,10 +12278,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="B82" t="s" s="2">
         <v>569</v>
-      </c>
-      <c r="B82" t="s" s="2">
-        <v>570</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12400,10 +12396,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="B83" t="s" s="2">
         <v>571</v>
-      </c>
-      <c r="B83" t="s" s="2">
-        <v>572</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12520,10 +12516,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
+        <v>572</v>
+      </c>
+      <c r="B84" t="s" s="2">
         <v>573</v>
-      </c>
-      <c r="B84" t="s" s="2">
-        <v>574</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12549,10 +12545,10 @@
         <v>217</v>
       </c>
       <c r="L84" t="s" s="2">
+        <v>574</v>
+      </c>
+      <c r="M84" t="s" s="2">
         <v>575</v>
-      </c>
-      <c r="M84" t="s" s="2">
-        <v>576</v>
       </c>
       <c r="N84" t="s" s="2">
         <v>220</v>
@@ -12595,7 +12591,7 @@
         <v>20</v>
       </c>
       <c r="AB84" t="s" s="2">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="AC84" s="2"/>
       <c r="AD84" t="s" s="2">
@@ -12640,13 +12636,13 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
+        <v>576</v>
+      </c>
+      <c r="B85" t="s" s="2">
+        <v>573</v>
+      </c>
+      <c r="C85" t="s" s="2">
         <v>577</v>
-      </c>
-      <c r="B85" t="s" s="2">
-        <v>574</v>
-      </c>
-      <c r="C85" t="s" s="2">
-        <v>578</v>
       </c>
       <c r="D85" t="s" s="2">
         <v>20</v>
@@ -12671,10 +12667,10 @@
         <v>217</v>
       </c>
       <c r="L85" t="s" s="2">
+        <v>574</v>
+      </c>
+      <c r="M85" t="s" s="2">
         <v>575</v>
-      </c>
-      <c r="M85" t="s" s="2">
-        <v>576</v>
       </c>
       <c r="N85" t="s" s="2">
         <v>220</v>
@@ -12764,10 +12760,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
+        <v>578</v>
+      </c>
+      <c r="B86" t="s" s="2">
         <v>579</v>
-      </c>
-      <c r="B86" t="s" s="2">
-        <v>580</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12882,10 +12878,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
+        <v>580</v>
+      </c>
+      <c r="B87" t="s" s="2">
         <v>581</v>
-      </c>
-      <c r="B87" t="s" s="2">
-        <v>582</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -13002,10 +12998,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
+        <v>582</v>
+      </c>
+      <c r="B88" t="s" s="2">
         <v>583</v>
-      </c>
-      <c r="B88" t="s" s="2">
-        <v>584</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13047,7 +13043,7 @@
       </c>
       <c r="Q88" s="2"/>
       <c r="R88" t="s" s="2">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="S88" t="s" s="2">
         <v>20</v>
@@ -13124,10 +13120,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
+        <v>584</v>
+      </c>
+      <c r="B89" t="s" s="2">
         <v>585</v>
-      </c>
-      <c r="B89" t="s" s="2">
-        <v>586</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13244,10 +13240,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
+        <v>586</v>
+      </c>
+      <c r="B90" t="s" s="2">
         <v>587</v>
-      </c>
-      <c r="B90" t="s" s="2">
-        <v>588</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13287,7 +13283,7 @@
       </c>
       <c r="Q90" s="2"/>
       <c r="R90" t="s" s="2">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="S90" t="s" s="2">
         <v>20</v>
@@ -13364,10 +13360,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
+        <v>589</v>
+      </c>
+      <c r="B91" t="s" s="2">
         <v>590</v>
-      </c>
-      <c r="B91" t="s" s="2">
-        <v>591</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13484,10 +13480,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
+        <v>591</v>
+      </c>
+      <c r="B92" t="s" s="2">
         <v>592</v>
-      </c>
-      <c r="B92" t="s" s="2">
-        <v>593</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13606,10 +13602,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
+        <v>593</v>
+      </c>
+      <c r="B93" t="s" s="2">
         <v>594</v>
-      </c>
-      <c r="B93" t="s" s="2">
-        <v>595</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13728,7 +13724,7 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="B94" t="s" s="2">
         <v>542</v>
@@ -13754,7 +13750,7 @@
         <v>93</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="L94" t="s" s="2">
         <v>544</v>
@@ -13766,7 +13762,7 @@
         <v>546</v>
       </c>
       <c r="O94" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>20</v>
@@ -13836,24 +13832,24 @@
         <v>550</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP94" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
+        <v>596</v>
+      </c>
+      <c r="B95" t="s" s="2">
         <v>597</v>
-      </c>
-      <c r="B95" t="s" s="2">
-        <v>598</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13968,10 +13964,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
+        <v>598</v>
+      </c>
+      <c r="B96" t="s" s="2">
         <v>599</v>
-      </c>
-      <c r="B96" t="s" s="2">
-        <v>600</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -14088,10 +14084,10 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="B97" t="s" s="2">
         <v>601</v>
-      </c>
-      <c r="B97" t="s" s="2">
-        <v>602</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14114,19 +14110,19 @@
         <v>93</v>
       </c>
       <c r="K97" t="s" s="2">
+        <v>602</v>
+      </c>
+      <c r="L97" t="s" s="2">
         <v>603</v>
       </c>
-      <c r="L97" t="s" s="2">
+      <c r="M97" t="s" s="2">
         <v>604</v>
       </c>
-      <c r="M97" t="s" s="2">
+      <c r="N97" t="s" s="2">
         <v>605</v>
       </c>
-      <c r="N97" t="s" s="2">
+      <c r="O97" t="s" s="2">
         <v>606</v>
-      </c>
-      <c r="O97" t="s" s="2">
-        <v>607</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>20</v>
@@ -14175,7 +14171,7 @@
         <v>20</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>80</v>
@@ -14196,10 +14192,10 @@
         <v>20</v>
       </c>
       <c r="AM97" t="s" s="2">
+        <v>608</v>
+      </c>
+      <c r="AN97" t="s" s="2">
         <v>609</v>
-      </c>
-      <c r="AN97" t="s" s="2">
-        <v>610</v>
       </c>
       <c r="AO97" t="s" s="2">
         <v>20</v>
@@ -14210,10 +14206,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
+        <v>610</v>
+      </c>
+      <c r="B98" t="s" s="2">
         <v>611</v>
-      </c>
-      <c r="B98" t="s" s="2">
-        <v>612</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14239,20 +14235,20 @@
         <v>112</v>
       </c>
       <c r="L98" t="s" s="2">
+        <v>612</v>
+      </c>
+      <c r="M98" t="s" s="2">
         <v>613</v>
-      </c>
-      <c r="M98" t="s" s="2">
-        <v>614</v>
       </c>
       <c r="N98" s="2"/>
       <c r="O98" t="s" s="2">
+        <v>614</v>
+      </c>
+      <c r="P98" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q98" t="s" s="2">
         <v>615</v>
-      </c>
-      <c r="P98" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q98" t="s" s="2">
-        <v>616</v>
       </c>
       <c r="R98" t="s" s="2">
         <v>20</v>
@@ -14276,28 +14272,28 @@
         <v>181</v>
       </c>
       <c r="Y98" t="s" s="2">
+        <v>616</v>
+      </c>
+      <c r="Z98" t="s" s="2">
         <v>617</v>
       </c>
-      <c r="Z98" t="s" s="2">
+      <c r="AA98" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB98" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC98" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD98" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE98" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF98" t="s" s="2">
         <v>618</v>
-      </c>
-      <c r="AA98" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB98" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC98" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD98" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE98" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF98" t="s" s="2">
-        <v>619</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>80</v>
@@ -14318,10 +14314,10 @@
         <v>20</v>
       </c>
       <c r="AM98" t="s" s="2">
+        <v>619</v>
+      </c>
+      <c r="AN98" t="s" s="2">
         <v>620</v>
-      </c>
-      <c r="AN98" t="s" s="2">
-        <v>621</v>
       </c>
       <c r="AO98" t="s" s="2">
         <v>20</v>
@@ -14332,10 +14328,10 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
+        <v>621</v>
+      </c>
+      <c r="B99" t="s" s="2">
         <v>622</v>
-      </c>
-      <c r="B99" t="s" s="2">
-        <v>623</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14361,14 +14357,14 @@
         <v>204</v>
       </c>
       <c r="L99" t="s" s="2">
+        <v>623</v>
+      </c>
+      <c r="M99" t="s" s="2">
         <v>624</v>
-      </c>
-      <c r="M99" t="s" s="2">
-        <v>625</v>
       </c>
       <c r="N99" s="2"/>
       <c r="O99" t="s" s="2">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="P99" t="s" s="2">
         <v>20</v>
@@ -14417,7 +14413,7 @@
         <v>20</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>80</v>
@@ -14438,10 +14434,10 @@
         <v>20</v>
       </c>
       <c r="AM99" t="s" s="2">
+        <v>627</v>
+      </c>
+      <c r="AN99" t="s" s="2">
         <v>628</v>
-      </c>
-      <c r="AN99" t="s" s="2">
-        <v>629</v>
       </c>
       <c r="AO99" t="s" s="2">
         <v>20</v>
@@ -14452,10 +14448,10 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
+        <v>629</v>
+      </c>
+      <c r="B100" t="s" s="2">
         <v>630</v>
-      </c>
-      <c r="B100" t="s" s="2">
-        <v>631</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14481,72 +14477,72 @@
         <v>106</v>
       </c>
       <c r="L100" t="s" s="2">
+        <v>631</v>
+      </c>
+      <c r="M100" t="s" s="2">
         <v>632</v>
-      </c>
-      <c r="M100" t="s" s="2">
-        <v>633</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" t="s" s="2">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>20</v>
       </c>
       <c r="Q100" s="2"/>
       <c r="R100" t="s" s="2">
+        <v>634</v>
+      </c>
+      <c r="S100" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T100" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U100" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V100" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W100" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X100" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y100" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z100" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA100" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB100" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC100" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD100" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE100" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF100" t="s" s="2">
         <v>635</v>
       </c>
-      <c r="S100" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T100" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U100" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V100" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W100" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X100" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y100" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z100" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA100" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB100" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC100" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD100" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE100" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF100" t="s" s="2">
+      <c r="AG100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH100" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI100" t="s" s="2">
         <v>636</v>
-      </c>
-      <c r="AG100" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH100" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AI100" t="s" s="2">
-        <v>637</v>
       </c>
       <c r="AJ100" t="s" s="2">
         <v>104</v>
@@ -14558,10 +14554,10 @@
         <v>20</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="AN100" t="s" s="2">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="AO100" t="s" s="2">
         <v>20</v>
@@ -14572,10 +14568,10 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
+        <v>638</v>
+      </c>
+      <c r="B101" t="s" s="2">
         <v>639</v>
-      </c>
-      <c r="B101" t="s" s="2">
-        <v>640</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14601,65 +14597,65 @@
         <v>112</v>
       </c>
       <c r="L101" t="s" s="2">
+        <v>640</v>
+      </c>
+      <c r="M101" t="s" s="2">
+        <v>640</v>
+      </c>
+      <c r="N101" t="s" s="2">
         <v>641</v>
       </c>
-      <c r="M101" t="s" s="2">
-        <v>641</v>
-      </c>
-      <c r="N101" t="s" s="2">
+      <c r="O101" t="s" s="2">
         <v>642</v>
-      </c>
-      <c r="O101" t="s" s="2">
-        <v>643</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>20</v>
       </c>
       <c r="Q101" s="2"/>
       <c r="R101" t="s" s="2">
+        <v>643</v>
+      </c>
+      <c r="S101" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T101" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U101" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V101" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W101" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X101" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y101" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z101" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA101" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB101" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC101" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD101" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE101" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF101" t="s" s="2">
         <v>644</v>
-      </c>
-      <c r="S101" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T101" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U101" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V101" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W101" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X101" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y101" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z101" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA101" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB101" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC101" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD101" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE101" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF101" t="s" s="2">
-        <v>645</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>80</v>
@@ -14680,10 +14676,10 @@
         <v>20</v>
       </c>
       <c r="AM101" t="s" s="2">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="AN101" t="s" s="2">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="AO101" t="s" s="2">
         <v>20</v>
@@ -14694,7 +14690,7 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="B102" t="s" s="2">
         <v>551</v>
@@ -14732,7 +14728,7 @@
         <v>554</v>
       </c>
       <c r="O102" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="P102" t="s" s="2">
         <v>20</v>
@@ -14760,10 +14756,10 @@
         <v>290</v>
       </c>
       <c r="Y102" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="Z102" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="AA102" t="s" s="2">
         <v>20</v>
@@ -14805,7 +14801,7 @@
         <v>135</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="AO102" t="s" s="2">
         <v>20</v>
@@ -14816,14 +14812,14 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="B103" t="s" s="2">
         <v>556</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="E103" s="2"/>
       <c r="F103" t="s" s="2">
@@ -14845,16 +14841,16 @@
         <v>189</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="O103" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>20</v>
@@ -14882,10 +14878,10 @@
         <v>290</v>
       </c>
       <c r="Y103" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="Z103" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="AA103" t="s" s="2">
         <v>20</v>
@@ -14921,24 +14917,24 @@
         <v>20</v>
       </c>
       <c r="AL103" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="AM103" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="AO103" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP103" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="B104" t="s" s="2">
         <v>557</v>
@@ -14973,10 +14969,10 @@
         <v>559</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="O104" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="P104" t="s" s="2">
         <v>20</v>
@@ -15046,10 +15042,10 @@
         <v>20</v>
       </c>
       <c r="AM104" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="AN104" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="AO104" t="s" s="2">
         <v>20</v>
@@ -15060,13 +15056,13 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
+        <v>649</v>
+      </c>
+      <c r="B105" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="C105" t="s" s="2">
         <v>650</v>
-      </c>
-      <c r="B105" t="s" s="2">
-        <v>522</v>
-      </c>
-      <c r="C105" t="s" s="2">
-        <v>651</v>
       </c>
       <c r="D105" t="s" s="2">
         <v>20</v>
@@ -15088,19 +15084,19 @@
         <v>93</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="O105" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="P105" t="s" s="2">
         <v>20</v>
@@ -15149,7 +15145,7 @@
         <v>20</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>80</v>
@@ -15161,7 +15157,7 @@
         <v>20</v>
       </c>
       <c r="AJ105" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="AK105" t="s" s="2">
         <v>20</v>
@@ -15170,10 +15166,10 @@
         <v>20</v>
       </c>
       <c r="AM105" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="AN105" t="s" s="2">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="AO105" t="s" s="2">
         <v>20</v>
@@ -15184,10 +15180,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -15302,10 +15298,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15422,14 +15418,14 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="E108" s="2"/>
       <c r="F108" t="s" s="2">
@@ -15451,10 +15447,10 @@
         <v>138</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="N108" t="s" s="2">
         <v>141</v>
@@ -15509,7 +15505,7 @@
         <v>20</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>80</v>
@@ -15544,10 +15540,10 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15573,16 +15569,16 @@
         <v>189</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>568</v>
+        <v>288</v>
       </c>
       <c r="O109" t="s" s="2">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="P109" t="s" s="2">
         <v>20</v>
@@ -15631,7 +15627,7 @@
         <v>20</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>92</v>
@@ -15649,16 +15645,16 @@
         <v>20</v>
       </c>
       <c r="AL109" t="s" s="2">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="AM109" t="s" s="2">
-        <v>334</v>
+        <v>295</v>
       </c>
       <c r="AN109" t="s" s="2">
-        <v>540</v>
+        <v>296</v>
       </c>
       <c r="AO109" t="s" s="2">
-        <v>541</v>
+        <v>297</v>
       </c>
       <c r="AP109" t="s" s="2">
         <v>20</v>
@@ -15666,10 +15662,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15784,10 +15780,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15904,10 +15900,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -15933,10 +15929,10 @@
         <v>217</v>
       </c>
       <c r="L112" t="s" s="2">
+        <v>659</v>
+      </c>
+      <c r="M112" t="s" s="2">
         <v>660</v>
-      </c>
-      <c r="M112" t="s" s="2">
-        <v>661</v>
       </c>
       <c r="N112" t="s" s="2">
         <v>220</v>
@@ -15979,7 +15975,7 @@
         <v>20</v>
       </c>
       <c r="AB112" t="s" s="2">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="AC112" s="2"/>
       <c r="AD112" t="s" s="2">
@@ -16024,13 +16020,13 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
+        <v>661</v>
+      </c>
+      <c r="B113" t="s" s="2">
+        <v>573</v>
+      </c>
+      <c r="C113" t="s" s="2">
         <v>662</v>
-      </c>
-      <c r="B113" t="s" s="2">
-        <v>574</v>
-      </c>
-      <c r="C113" t="s" s="2">
-        <v>663</v>
       </c>
       <c r="D113" t="s" s="2">
         <v>20</v>
@@ -16055,10 +16051,10 @@
         <v>217</v>
       </c>
       <c r="L113" t="s" s="2">
+        <v>659</v>
+      </c>
+      <c r="M113" t="s" s="2">
         <v>660</v>
-      </c>
-      <c r="M113" t="s" s="2">
-        <v>661</v>
       </c>
       <c r="N113" t="s" s="2">
         <v>220</v>
@@ -16148,10 +16144,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -16266,10 +16262,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -16386,10 +16382,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -16431,7 +16427,7 @@
       </c>
       <c r="Q116" s="2"/>
       <c r="R116" t="s" s="2">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="S116" t="s" s="2">
         <v>20</v>
@@ -16508,10 +16504,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -16628,10 +16624,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -16671,7 +16667,7 @@
       </c>
       <c r="Q118" s="2"/>
       <c r="R118" t="s" s="2">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="S118" t="s" s="2">
         <v>20</v>
@@ -16748,10 +16744,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -16868,10 +16864,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -16990,10 +16986,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -17112,7 +17108,7 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="B122" t="s" s="2">
         <v>542</v>
@@ -17138,7 +17134,7 @@
         <v>93</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="L122" t="s" s="2">
         <v>544</v>
@@ -17150,7 +17146,7 @@
         <v>546</v>
       </c>
       <c r="O122" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="P122" t="s" s="2">
         <v>20</v>
@@ -17220,24 +17216,24 @@
         <v>550</v>
       </c>
       <c r="AM122" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="AN122" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="AO122" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP122" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -17352,10 +17348,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -17472,10 +17468,10 @@
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -17498,19 +17494,19 @@
         <v>93</v>
       </c>
       <c r="K125" t="s" s="2">
+        <v>602</v>
+      </c>
+      <c r="L125" t="s" s="2">
         <v>603</v>
       </c>
-      <c r="L125" t="s" s="2">
+      <c r="M125" t="s" s="2">
         <v>604</v>
       </c>
-      <c r="M125" t="s" s="2">
+      <c r="N125" t="s" s="2">
         <v>605</v>
       </c>
-      <c r="N125" t="s" s="2">
+      <c r="O125" t="s" s="2">
         <v>606</v>
-      </c>
-      <c r="O125" t="s" s="2">
-        <v>607</v>
       </c>
       <c r="P125" t="s" s="2">
         <v>20</v>
@@ -17559,7 +17555,7 @@
         <v>20</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>80</v>
@@ -17580,10 +17576,10 @@
         <v>20</v>
       </c>
       <c r="AM125" t="s" s="2">
+        <v>608</v>
+      </c>
+      <c r="AN125" t="s" s="2">
         <v>609</v>
-      </c>
-      <c r="AN125" t="s" s="2">
-        <v>610</v>
       </c>
       <c r="AO125" t="s" s="2">
         <v>20</v>
@@ -17594,10 +17590,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -17623,20 +17619,20 @@
         <v>112</v>
       </c>
       <c r="L126" t="s" s="2">
+        <v>612</v>
+      </c>
+      <c r="M126" t="s" s="2">
         <v>613</v>
-      </c>
-      <c r="M126" t="s" s="2">
-        <v>614</v>
       </c>
       <c r="N126" s="2"/>
       <c r="O126" t="s" s="2">
+        <v>614</v>
+      </c>
+      <c r="P126" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q126" t="s" s="2">
         <v>615</v>
-      </c>
-      <c r="P126" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q126" t="s" s="2">
-        <v>616</v>
       </c>
       <c r="R126" t="s" s="2">
         <v>20</v>
@@ -17660,28 +17656,28 @@
         <v>181</v>
       </c>
       <c r="Y126" t="s" s="2">
+        <v>616</v>
+      </c>
+      <c r="Z126" t="s" s="2">
         <v>617</v>
       </c>
-      <c r="Z126" t="s" s="2">
+      <c r="AA126" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB126" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC126" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD126" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE126" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF126" t="s" s="2">
         <v>618</v>
-      </c>
-      <c r="AA126" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB126" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC126" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD126" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE126" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF126" t="s" s="2">
-        <v>619</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>80</v>
@@ -17702,10 +17698,10 @@
         <v>20</v>
       </c>
       <c r="AM126" t="s" s="2">
+        <v>619</v>
+      </c>
+      <c r="AN126" t="s" s="2">
         <v>620</v>
-      </c>
-      <c r="AN126" t="s" s="2">
-        <v>621</v>
       </c>
       <c r="AO126" t="s" s="2">
         <v>20</v>
@@ -17716,10 +17712,10 @@
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -17745,14 +17741,14 @@
         <v>204</v>
       </c>
       <c r="L127" t="s" s="2">
+        <v>623</v>
+      </c>
+      <c r="M127" t="s" s="2">
         <v>624</v>
-      </c>
-      <c r="M127" t="s" s="2">
-        <v>625</v>
       </c>
       <c r="N127" s="2"/>
       <c r="O127" t="s" s="2">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="P127" t="s" s="2">
         <v>20</v>
@@ -17801,7 +17797,7 @@
         <v>20</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>80</v>
@@ -17822,10 +17818,10 @@
         <v>20</v>
       </c>
       <c r="AM127" t="s" s="2">
+        <v>627</v>
+      </c>
+      <c r="AN127" t="s" s="2">
         <v>628</v>
-      </c>
-      <c r="AN127" t="s" s="2">
-        <v>629</v>
       </c>
       <c r="AO127" t="s" s="2">
         <v>20</v>
@@ -17836,10 +17832,10 @@
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -17865,72 +17861,72 @@
         <v>106</v>
       </c>
       <c r="L128" t="s" s="2">
+        <v>631</v>
+      </c>
+      <c r="M128" t="s" s="2">
         <v>632</v>
-      </c>
-      <c r="M128" t="s" s="2">
-        <v>633</v>
       </c>
       <c r="N128" s="2"/>
       <c r="O128" t="s" s="2">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="P128" t="s" s="2">
         <v>20</v>
       </c>
       <c r="Q128" s="2"/>
       <c r="R128" t="s" s="2">
+        <v>634</v>
+      </c>
+      <c r="S128" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T128" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U128" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V128" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W128" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X128" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y128" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z128" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA128" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB128" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC128" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD128" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE128" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF128" t="s" s="2">
         <v>635</v>
       </c>
-      <c r="S128" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T128" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U128" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V128" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W128" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X128" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y128" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z128" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA128" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB128" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC128" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD128" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE128" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF128" t="s" s="2">
+      <c r="AG128" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH128" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI128" t="s" s="2">
         <v>636</v>
-      </c>
-      <c r="AG128" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH128" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AI128" t="s" s="2">
-        <v>637</v>
       </c>
       <c r="AJ128" t="s" s="2">
         <v>104</v>
@@ -17942,10 +17938,10 @@
         <v>20</v>
       </c>
       <c r="AM128" t="s" s="2">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="AN128" t="s" s="2">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="AO128" t="s" s="2">
         <v>20</v>
@@ -17956,10 +17952,10 @@
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -17985,65 +17981,65 @@
         <v>112</v>
       </c>
       <c r="L129" t="s" s="2">
+        <v>640</v>
+      </c>
+      <c r="M129" t="s" s="2">
+        <v>640</v>
+      </c>
+      <c r="N129" t="s" s="2">
         <v>641</v>
       </c>
-      <c r="M129" t="s" s="2">
-        <v>641</v>
-      </c>
-      <c r="N129" t="s" s="2">
+      <c r="O129" t="s" s="2">
         <v>642</v>
-      </c>
-      <c r="O129" t="s" s="2">
-        <v>643</v>
       </c>
       <c r="P129" t="s" s="2">
         <v>20</v>
       </c>
       <c r="Q129" s="2"/>
       <c r="R129" t="s" s="2">
+        <v>643</v>
+      </c>
+      <c r="S129" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T129" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U129" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V129" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W129" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X129" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y129" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z129" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA129" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB129" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC129" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD129" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE129" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF129" t="s" s="2">
         <v>644</v>
-      </c>
-      <c r="S129" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T129" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U129" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V129" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W129" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X129" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y129" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z129" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA129" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB129" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC129" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD129" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE129" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF129" t="s" s="2">
-        <v>645</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>80</v>
@@ -18064,10 +18060,10 @@
         <v>20</v>
       </c>
       <c r="AM129" t="s" s="2">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="AN129" t="s" s="2">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="AO129" t="s" s="2">
         <v>20</v>
@@ -18078,7 +18074,7 @@
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="B130" t="s" s="2">
         <v>551</v>
@@ -18116,7 +18112,7 @@
         <v>554</v>
       </c>
       <c r="O130" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="P130" t="s" s="2">
         <v>20</v>
@@ -18144,10 +18140,10 @@
         <v>290</v>
       </c>
       <c r="Y130" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="Z130" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="AA130" t="s" s="2">
         <v>20</v>
@@ -18189,7 +18185,7 @@
         <v>135</v>
       </c>
       <c r="AN130" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="AO130" t="s" s="2">
         <v>20</v>
@@ -18200,14 +18196,14 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="B131" t="s" s="2">
         <v>556</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="E131" s="2"/>
       <c r="F131" t="s" s="2">
@@ -18229,16 +18225,16 @@
         <v>189</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="N131" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="O131" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="P131" t="s" s="2">
         <v>20</v>
@@ -18266,10 +18262,10 @@
         <v>290</v>
       </c>
       <c r="Y131" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="Z131" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="AA131" t="s" s="2">
         <v>20</v>
@@ -18305,24 +18301,24 @@
         <v>20</v>
       </c>
       <c r="AL131" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="AM131" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="AN131" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="AO131" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP131" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="B132" t="s" s="2">
         <v>557</v>
@@ -18357,10 +18353,10 @@
         <v>559</v>
       </c>
       <c r="N132" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="O132" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="P132" t="s" s="2">
         <v>20</v>
@@ -18430,10 +18426,10 @@
         <v>20</v>
       </c>
       <c r="AM132" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="AN132" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="AO132" t="s" s="2">
         <v>20</v>

--- a/docs/StructureDefinition-PASportObservationBloodPressure.xlsx
+++ b/docs/StructureDefinition-PASportObservationBloodPressure.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-02T13:32:15+08:00</t>
+    <t>2026-04-03T21:17:06+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-PASportObservationBloodPressure.xlsx
+++ b/docs/StructureDefinition-PASportObservationBloodPressure.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-03T21:17:06+08:00</t>
+    <t>2026-06-25T08:48:04+08:00</t>
   </si>
   <si>
     <t>Publisher</t>
